--- a/molecular/primer_design/primer_master_summary_mem_highlighted.xlsx
+++ b/molecular/primer_design/primer_master_summary_mem_highlighted.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calum\OneDrive\Desktop\seaweeDNA\molecular\primer_design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{345AF82C-F3D9-4210-A5FC-78B51E8CFA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757A0EBA-7AFE-4B28-BC03-5A97BDA47C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5220" yWindow="-16500" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="primers" sheetId="1" r:id="rId1"/>
@@ -400,7 +400,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -409,9 +409,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -447,48 +444,36 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="22" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -815,9 +800,8 @@
     <col min="19" max="19" width="11.73046875" style="3" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="17.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9.06640625" style="3" customWidth="1"/>
-    <col min="22" max="22" width="75.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="23" max="73" width="9.06640625" style="4"/>
-    <col min="74" max="16384" width="9.06640625" style="3"/>
+    <col min="22" max="22" width="75.9296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.06640625" style="3"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:73" x14ac:dyDescent="0.45">
@@ -884,126 +868,126 @@
       <c r="U2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="V2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:73" s="7" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:73" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>20</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
         <v>20</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <v>60</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>58</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="4">
         <v>2</v>
       </c>
-      <c r="J3" s="5">
-        <v>55</v>
-      </c>
-      <c r="K3" s="6">
-        <v>55</v>
-      </c>
-      <c r="L3" s="6">
-        <v>55</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-      <c r="N3" s="5">
-        <v>0</v>
-      </c>
-      <c r="O3" s="5">
-        <v>0</v>
-      </c>
-      <c r="P3" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>3</v>
-      </c>
-      <c r="R3" s="5">
+      <c r="J3" s="4">
+        <v>55</v>
+      </c>
+      <c r="K3" s="5">
+        <v>55</v>
+      </c>
+      <c r="L3" s="5">
+        <v>55</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>3</v>
+      </c>
+      <c r="R3" s="4">
         <v>75</v>
       </c>
-      <c r="S3" s="6">
+      <c r="S3" s="5">
         <v>10.5</v>
       </c>
-      <c r="T3" s="5">
-        <v>3</v>
-      </c>
-      <c r="U3" s="5" t="s">
+      <c r="T3" s="4">
+        <v>3</v>
+      </c>
+      <c r="U3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="4"/>
-      <c r="AD3" s="4"/>
-      <c r="AE3" s="4"/>
-      <c r="AF3" s="4"/>
-      <c r="AG3" s="4"/>
-      <c r="AH3" s="4"/>
-      <c r="AI3" s="4"/>
-      <c r="AJ3" s="4"/>
-      <c r="AK3" s="4"/>
-      <c r="AL3" s="4"/>
-      <c r="AM3" s="4"/>
-      <c r="AN3" s="4"/>
-      <c r="AO3" s="4"/>
-      <c r="AP3" s="4"/>
-      <c r="AQ3" s="4"/>
-      <c r="AR3" s="4"/>
-      <c r="AS3" s="4"/>
-      <c r="AT3" s="4"/>
-      <c r="AU3" s="4"/>
-      <c r="AV3" s="4"/>
-      <c r="AW3" s="4"/>
-      <c r="AX3" s="4"/>
-      <c r="AY3" s="4"/>
-      <c r="AZ3" s="4"/>
-      <c r="BA3" s="4"/>
-      <c r="BB3" s="4"/>
-      <c r="BC3" s="4"/>
-      <c r="BD3" s="4"/>
-      <c r="BE3" s="4"/>
-      <c r="BF3" s="4"/>
-      <c r="BG3" s="4"/>
-      <c r="BH3" s="4"/>
-      <c r="BI3" s="4"/>
-      <c r="BJ3" s="4"/>
-      <c r="BK3" s="4"/>
-      <c r="BL3" s="4"/>
-      <c r="BM3" s="4"/>
-      <c r="BN3" s="4"/>
-      <c r="BO3" s="4"/>
-      <c r="BP3" s="4"/>
-      <c r="BQ3" s="4"/>
-      <c r="BR3" s="4"/>
-      <c r="BS3" s="4"/>
-      <c r="BT3" s="4"/>
-      <c r="BU3" s="4"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="3"/>
+      <c r="AK3" s="3"/>
+      <c r="AL3" s="3"/>
+      <c r="AM3" s="3"/>
+      <c r="AN3" s="3"/>
+      <c r="AO3" s="3"/>
+      <c r="AP3" s="3"/>
+      <c r="AQ3" s="3"/>
+      <c r="AR3" s="3"/>
+      <c r="AS3" s="3"/>
+      <c r="AT3" s="3"/>
+      <c r="AU3" s="3"/>
+      <c r="AV3" s="3"/>
+      <c r="AW3" s="3"/>
+      <c r="AX3" s="3"/>
+      <c r="AY3" s="3"/>
+      <c r="AZ3" s="3"/>
+      <c r="BA3" s="3"/>
+      <c r="BB3" s="3"/>
+      <c r="BC3" s="3"/>
+      <c r="BD3" s="3"/>
+      <c r="BE3" s="3"/>
+      <c r="BF3" s="3"/>
+      <c r="BG3" s="3"/>
+      <c r="BH3" s="3"/>
+      <c r="BI3" s="3"/>
+      <c r="BJ3" s="3"/>
+      <c r="BK3" s="3"/>
+      <c r="BL3" s="3"/>
+      <c r="BM3" s="3"/>
+      <c r="BN3" s="3"/>
+      <c r="BO3" s="3"/>
+      <c r="BP3" s="3"/>
+      <c r="BQ3" s="3"/>
+      <c r="BR3" s="3"/>
+      <c r="BS3" s="3"/>
+      <c r="BT3" s="3"/>
+      <c r="BU3" s="3"/>
     </row>
     <row r="4" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
@@ -1036,10 +1020,10 @@
       <c r="J4" s="3">
         <v>55</v>
       </c>
-      <c r="K4" s="8">
-        <v>55</v>
-      </c>
-      <c r="L4" s="8">
+      <c r="K4" s="7">
+        <v>55</v>
+      </c>
+      <c r="L4" s="7">
         <v>55</v>
       </c>
       <c r="M4" s="3">
@@ -1060,7 +1044,7 @@
       <c r="R4" s="3">
         <v>75</v>
       </c>
-      <c r="S4" s="8">
+      <c r="S4" s="7">
         <v>10.5</v>
       </c>
       <c r="T4" s="3">
@@ -1098,10 +1082,10 @@
       <c r="J5" s="3">
         <v>55</v>
       </c>
-      <c r="K5" s="8">
-        <v>55</v>
-      </c>
-      <c r="L5" s="8">
+      <c r="K5" s="7">
+        <v>55</v>
+      </c>
+      <c r="L5" s="7">
         <v>55</v>
       </c>
       <c r="M5" s="3">
@@ -1122,7 +1106,7 @@
       <c r="R5" s="3">
         <v>75</v>
       </c>
-      <c r="S5" s="8">
+      <c r="S5" s="7">
         <v>10.5</v>
       </c>
       <c r="T5" s="3">
@@ -1160,10 +1144,10 @@
       <c r="J6" s="3">
         <v>51</v>
       </c>
-      <c r="K6" s="8">
-        <v>55</v>
-      </c>
-      <c r="L6" s="8">
+      <c r="K6" s="7">
+        <v>55</v>
+      </c>
+      <c r="L6" s="7">
         <v>52.631578949999998</v>
       </c>
       <c r="M6" s="3">
@@ -1184,7 +1168,7 @@
       <c r="R6" s="3">
         <v>74</v>
       </c>
-      <c r="S6" s="8">
+      <c r="S6" s="7">
         <v>14.5</v>
       </c>
       <c r="T6" s="3">
@@ -1222,10 +1206,10 @@
       <c r="J7" s="3">
         <v>51</v>
       </c>
-      <c r="K7" s="8">
-        <v>55</v>
-      </c>
-      <c r="L7" s="8">
+      <c r="K7" s="7">
+        <v>55</v>
+      </c>
+      <c r="L7" s="7">
         <v>52.631578949999998</v>
       </c>
       <c r="M7" s="3">
@@ -1246,129 +1230,129 @@
       <c r="R7" s="3">
         <v>110</v>
       </c>
-      <c r="S7" s="8">
+      <c r="S7" s="7">
         <v>11.5</v>
       </c>
       <c r="T7" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:73" s="11" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:73" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="C8" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <v>20</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <v>20</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>60</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <v>58</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="8">
         <v>2</v>
       </c>
-      <c r="J8" s="9">
-        <v>55</v>
-      </c>
-      <c r="K8" s="10">
-        <v>55</v>
-      </c>
-      <c r="L8" s="10">
-        <v>55</v>
-      </c>
-      <c r="M8" s="9">
-        <v>0</v>
-      </c>
-      <c r="N8" s="9">
-        <v>3</v>
-      </c>
-      <c r="O8" s="9">
-        <v>0</v>
-      </c>
-      <c r="P8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>0</v>
-      </c>
-      <c r="R8" s="9">
+      <c r="J8" s="8">
+        <v>55</v>
+      </c>
+      <c r="K8" s="9">
+        <v>55</v>
+      </c>
+      <c r="L8" s="9">
+        <v>55</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0</v>
+      </c>
+      <c r="N8" s="8">
+        <v>3</v>
+      </c>
+      <c r="O8" s="8">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
         <v>111</v>
       </c>
-      <c r="S8" s="10">
+      <c r="S8" s="9">
         <v>7.5</v>
       </c>
-      <c r="T8" s="9">
+      <c r="T8" s="8">
         <v>1</v>
       </c>
-      <c r="U8" s="9" t="s">
+      <c r="U8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
-      <c r="AB8" s="4"/>
-      <c r="AC8" s="4"/>
-      <c r="AD8" s="4"/>
-      <c r="AE8" s="4"/>
-      <c r="AF8" s="4"/>
-      <c r="AG8" s="4"/>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="4"/>
-      <c r="AJ8" s="4"/>
-      <c r="AK8" s="4"/>
-      <c r="AL8" s="4"/>
-      <c r="AM8" s="4"/>
-      <c r="AN8" s="4"/>
-      <c r="AO8" s="4"/>
-      <c r="AP8" s="4"/>
-      <c r="AQ8" s="4"/>
-      <c r="AR8" s="4"/>
-      <c r="AS8" s="4"/>
-      <c r="AT8" s="4"/>
-      <c r="AU8" s="4"/>
-      <c r="AV8" s="4"/>
-      <c r="AW8" s="4"/>
-      <c r="AX8" s="4"/>
-      <c r="AY8" s="4"/>
-      <c r="AZ8" s="4"/>
-      <c r="BA8" s="4"/>
-      <c r="BB8" s="4"/>
-      <c r="BC8" s="4"/>
-      <c r="BD8" s="4"/>
-      <c r="BE8" s="4"/>
-      <c r="BF8" s="4"/>
-      <c r="BG8" s="4"/>
-      <c r="BH8" s="4"/>
-      <c r="BI8" s="4"/>
-      <c r="BJ8" s="4"/>
-      <c r="BK8" s="4"/>
-      <c r="BL8" s="4"/>
-      <c r="BM8" s="4"/>
-      <c r="BN8" s="4"/>
-      <c r="BO8" s="4"/>
-      <c r="BP8" s="4"/>
-      <c r="BQ8" s="4"/>
-      <c r="BR8" s="4"/>
-      <c r="BS8" s="4"/>
-      <c r="BT8" s="4"/>
-      <c r="BU8" s="4"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="3"/>
+      <c r="AI8" s="3"/>
+      <c r="AJ8" s="3"/>
+      <c r="AK8" s="3"/>
+      <c r="AL8" s="3"/>
+      <c r="AM8" s="3"/>
+      <c r="AN8" s="3"/>
+      <c r="AO8" s="3"/>
+      <c r="AP8" s="3"/>
+      <c r="AQ8" s="3"/>
+      <c r="AR8" s="3"/>
+      <c r="AS8" s="3"/>
+      <c r="AT8" s="3"/>
+      <c r="AU8" s="3"/>
+      <c r="AV8" s="3"/>
+      <c r="AW8" s="3"/>
+      <c r="AX8" s="3"/>
+      <c r="AY8" s="3"/>
+      <c r="AZ8" s="3"/>
+      <c r="BA8" s="3"/>
+      <c r="BB8" s="3"/>
+      <c r="BC8" s="3"/>
+      <c r="BD8" s="3"/>
+      <c r="BE8" s="3"/>
+      <c r="BF8" s="3"/>
+      <c r="BG8" s="3"/>
+      <c r="BH8" s="3"/>
+      <c r="BI8" s="3"/>
+      <c r="BJ8" s="3"/>
+      <c r="BK8" s="3"/>
+      <c r="BL8" s="3"/>
+      <c r="BM8" s="3"/>
+      <c r="BN8" s="3"/>
+      <c r="BO8" s="3"/>
+      <c r="BP8" s="3"/>
+      <c r="BQ8" s="3"/>
+      <c r="BR8" s="3"/>
+      <c r="BS8" s="3"/>
+      <c r="BT8" s="3"/>
+      <c r="BU8" s="3"/>
     </row>
     <row r="9" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
@@ -1401,10 +1385,10 @@
       <c r="J9" s="3">
         <v>51</v>
       </c>
-      <c r="K9" s="8">
-        <v>55</v>
-      </c>
-      <c r="L9" s="8">
+      <c r="K9" s="7">
+        <v>55</v>
+      </c>
+      <c r="L9" s="7">
         <v>52.631578949999998</v>
       </c>
       <c r="M9" s="3">
@@ -1425,7 +1409,7 @@
       <c r="R9" s="3">
         <v>110</v>
       </c>
-      <c r="S9" s="8">
+      <c r="S9" s="7">
         <v>11.5</v>
       </c>
       <c r="T9" s="3">
@@ -1463,10 +1447,10 @@
       <c r="J10" s="3">
         <v>51</v>
       </c>
-      <c r="K10" s="8">
-        <v>55</v>
-      </c>
-      <c r="L10" s="8">
+      <c r="K10" s="7">
+        <v>55</v>
+      </c>
+      <c r="L10" s="7">
         <v>52.631578949999998</v>
       </c>
       <c r="M10" s="3">
@@ -1487,129 +1471,129 @@
       <c r="R10" s="3">
         <v>110</v>
       </c>
-      <c r="S10" s="8">
+      <c r="S10" s="7">
         <v>11.5</v>
       </c>
       <c r="T10" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:73" s="14" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="12" t="s">
+    <row r="11" spans="1:73" s="13" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="12" t="s">
+      <c r="C11" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="11">
         <v>20</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="11">
         <v>20</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="11">
         <v>60</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="11">
         <v>58</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="11">
         <v>2</v>
       </c>
-      <c r="J11" s="12">
-        <v>55</v>
-      </c>
-      <c r="K11" s="13">
-        <v>55</v>
-      </c>
-      <c r="L11" s="13">
-        <v>55</v>
-      </c>
-      <c r="M11" s="12">
-        <v>0</v>
-      </c>
-      <c r="N11" s="12">
-        <v>3</v>
-      </c>
-      <c r="O11" s="12">
-        <v>0</v>
-      </c>
-      <c r="P11" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="12">
-        <v>0</v>
-      </c>
-      <c r="R11" s="12">
+      <c r="J11" s="11">
+        <v>55</v>
+      </c>
+      <c r="K11" s="12">
+        <v>55</v>
+      </c>
+      <c r="L11" s="12">
+        <v>55</v>
+      </c>
+      <c r="M11" s="11">
+        <v>0</v>
+      </c>
+      <c r="N11" s="11">
+        <v>3</v>
+      </c>
+      <c r="O11" s="11">
+        <v>0</v>
+      </c>
+      <c r="P11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
         <v>111</v>
       </c>
-      <c r="S11" s="13">
+      <c r="S11" s="12">
         <v>7.5</v>
       </c>
-      <c r="T11" s="12">
+      <c r="T11" s="11">
         <v>2</v>
       </c>
-      <c r="U11" s="12" t="s">
+      <c r="U11" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4"/>
-      <c r="AB11" s="4"/>
-      <c r="AC11" s="4"/>
-      <c r="AD11" s="4"/>
-      <c r="AE11" s="4"/>
-      <c r="AF11" s="4"/>
-      <c r="AG11" s="4"/>
-      <c r="AH11" s="4"/>
-      <c r="AI11" s="4"/>
-      <c r="AJ11" s="4"/>
-      <c r="AK11" s="4"/>
-      <c r="AL11" s="4"/>
-      <c r="AM11" s="4"/>
-      <c r="AN11" s="4"/>
-      <c r="AO11" s="4"/>
-      <c r="AP11" s="4"/>
-      <c r="AQ11" s="4"/>
-      <c r="AR11" s="4"/>
-      <c r="AS11" s="4"/>
-      <c r="AT11" s="4"/>
-      <c r="AU11" s="4"/>
-      <c r="AV11" s="4"/>
-      <c r="AW11" s="4"/>
-      <c r="AX11" s="4"/>
-      <c r="AY11" s="4"/>
-      <c r="AZ11" s="4"/>
-      <c r="BA11" s="4"/>
-      <c r="BB11" s="4"/>
-      <c r="BC11" s="4"/>
-      <c r="BD11" s="4"/>
-      <c r="BE11" s="4"/>
-      <c r="BF11" s="4"/>
-      <c r="BG11" s="4"/>
-      <c r="BH11" s="4"/>
-      <c r="BI11" s="4"/>
-      <c r="BJ11" s="4"/>
-      <c r="BK11" s="4"/>
-      <c r="BL11" s="4"/>
-      <c r="BM11" s="4"/>
-      <c r="BN11" s="4"/>
-      <c r="BO11" s="4"/>
-      <c r="BP11" s="4"/>
-      <c r="BQ11" s="4"/>
-      <c r="BR11" s="4"/>
-      <c r="BS11" s="4"/>
-      <c r="BT11" s="4"/>
-      <c r="BU11" s="4"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
+      <c r="AR11" s="3"/>
+      <c r="AS11" s="3"/>
+      <c r="AT11" s="3"/>
+      <c r="AU11" s="3"/>
+      <c r="AV11" s="3"/>
+      <c r="AW11" s="3"/>
+      <c r="AX11" s="3"/>
+      <c r="AY11" s="3"/>
+      <c r="AZ11" s="3"/>
+      <c r="BA11" s="3"/>
+      <c r="BB11" s="3"/>
+      <c r="BC11" s="3"/>
+      <c r="BD11" s="3"/>
+      <c r="BE11" s="3"/>
+      <c r="BF11" s="3"/>
+      <c r="BG11" s="3"/>
+      <c r="BH11" s="3"/>
+      <c r="BI11" s="3"/>
+      <c r="BJ11" s="3"/>
+      <c r="BK11" s="3"/>
+      <c r="BL11" s="3"/>
+      <c r="BM11" s="3"/>
+      <c r="BN11" s="3"/>
+      <c r="BO11" s="3"/>
+      <c r="BP11" s="3"/>
+      <c r="BQ11" s="3"/>
+      <c r="BR11" s="3"/>
+      <c r="BS11" s="3"/>
+      <c r="BT11" s="3"/>
+      <c r="BU11" s="3"/>
     </row>
     <row r="12" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
@@ -1642,10 +1626,10 @@
       <c r="J12" s="3">
         <v>51</v>
       </c>
-      <c r="K12" s="8">
-        <v>55</v>
-      </c>
-      <c r="L12" s="8">
+      <c r="K12" s="7">
+        <v>55</v>
+      </c>
+      <c r="L12" s="7">
         <v>52.631578949999998</v>
       </c>
       <c r="M12" s="3">
@@ -1666,7 +1650,7 @@
       <c r="R12" s="3">
         <v>110</v>
       </c>
-      <c r="S12" s="8">
+      <c r="S12" s="7">
         <v>11.5</v>
       </c>
       <c r="T12" s="3">
@@ -1704,10 +1688,10 @@
       <c r="J13" s="3">
         <v>57</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="7">
         <v>38.46153846</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="7">
         <v>45.454545449999998</v>
       </c>
       <c r="M13" s="3">
@@ -1725,7 +1709,7 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="S13" s="8">
+      <c r="S13" s="7">
         <v>26.76923077</v>
       </c>
       <c r="T13" s="3">
@@ -1763,10 +1747,10 @@
       <c r="J14" s="3">
         <v>59</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="7">
         <v>38.46153846</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="7">
         <v>43.47826087</v>
       </c>
       <c r="M14" s="3">
@@ -1784,7 +1768,7 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="8">
+      <c r="S14" s="7">
         <v>24.76923077</v>
       </c>
       <c r="T14" s="3">
@@ -1822,10 +1806,10 @@
       <c r="J15" s="3">
         <v>55</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="7">
         <v>38.46153846</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="7">
         <v>47.619047620000003</v>
       </c>
       <c r="M15" s="3">
@@ -1843,7 +1827,7 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="8">
+      <c r="S15" s="7">
         <v>28.76923077</v>
       </c>
       <c r="T15" s="3">
@@ -1881,10 +1865,10 @@
       <c r="J16" s="3">
         <v>55</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="7">
         <v>38.46153846</v>
       </c>
-      <c r="L16" s="8">
+      <c r="L16" s="7">
         <v>47.619047620000003</v>
       </c>
       <c r="M16" s="3">
@@ -1902,7 +1886,7 @@
       <c r="Q16" s="3">
         <v>0</v>
       </c>
-      <c r="S16" s="8">
+      <c r="S16" s="7">
         <v>28.76923077</v>
       </c>
       <c r="T16" s="3">
@@ -1940,10 +1924,10 @@
       <c r="J17" s="3">
         <v>57</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="7">
         <v>38.46153846</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L17" s="7">
         <v>45.454545449999998</v>
       </c>
       <c r="M17" s="3">
@@ -1961,242 +1945,242 @@
       <c r="Q17" s="3">
         <v>0</v>
       </c>
-      <c r="S17" s="8">
+      <c r="S17" s="7">
         <v>26.76923077</v>
       </c>
       <c r="T17" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:73" s="14" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="12" t="s">
+    <row r="18" spans="1:73" s="13" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="11">
         <v>26</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="11">
         <v>24</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="11">
         <v>68</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="11">
         <v>64</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="11">
         <v>4</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="11">
         <v>61</v>
       </c>
-      <c r="K18" s="13">
+      <c r="K18" s="12">
         <v>38.46153846</v>
       </c>
-      <c r="L18" s="13">
+      <c r="L18" s="12">
         <v>41.666666669999998</v>
       </c>
-      <c r="M18" s="12">
-        <v>3</v>
-      </c>
-      <c r="N18" s="12">
-        <v>0</v>
-      </c>
-      <c r="O18" s="12">
-        <v>0</v>
-      </c>
-      <c r="P18" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="12">
-        <v>0</v>
-      </c>
-      <c r="R18" s="12"/>
-      <c r="S18" s="13">
+      <c r="M18" s="11">
+        <v>3</v>
+      </c>
+      <c r="N18" s="11">
+        <v>0</v>
+      </c>
+      <c r="O18" s="11">
+        <v>0</v>
+      </c>
+      <c r="P18" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="11">
+        <v>0</v>
+      </c>
+      <c r="R18" s="11"/>
+      <c r="S18" s="12">
         <v>22.76923077</v>
       </c>
-      <c r="T18" s="12">
+      <c r="T18" s="11">
         <v>2</v>
       </c>
-      <c r="U18" s="12" t="s">
+      <c r="U18" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="4"/>
-      <c r="AA18" s="4"/>
-      <c r="AB18" s="4"/>
-      <c r="AC18" s="4"/>
-      <c r="AD18" s="4"/>
-      <c r="AE18" s="4"/>
-      <c r="AF18" s="4"/>
-      <c r="AG18" s="4"/>
-      <c r="AH18" s="4"/>
-      <c r="AI18" s="4"/>
-      <c r="AJ18" s="4"/>
-      <c r="AK18" s="4"/>
-      <c r="AL18" s="4"/>
-      <c r="AM18" s="4"/>
-      <c r="AN18" s="4"/>
-      <c r="AO18" s="4"/>
-      <c r="AP18" s="4"/>
-      <c r="AQ18" s="4"/>
-      <c r="AR18" s="4"/>
-      <c r="AS18" s="4"/>
-      <c r="AT18" s="4"/>
-      <c r="AU18" s="4"/>
-      <c r="AV18" s="4"/>
-      <c r="AW18" s="4"/>
-      <c r="AX18" s="4"/>
-      <c r="AY18" s="4"/>
-      <c r="AZ18" s="4"/>
-      <c r="BA18" s="4"/>
-      <c r="BB18" s="4"/>
-      <c r="BC18" s="4"/>
-      <c r="BD18" s="4"/>
-      <c r="BE18" s="4"/>
-      <c r="BF18" s="4"/>
-      <c r="BG18" s="4"/>
-      <c r="BH18" s="4"/>
-      <c r="BI18" s="4"/>
-      <c r="BJ18" s="4"/>
-      <c r="BK18" s="4"/>
-      <c r="BL18" s="4"/>
-      <c r="BM18" s="4"/>
-      <c r="BN18" s="4"/>
-      <c r="BO18" s="4"/>
-      <c r="BP18" s="4"/>
-      <c r="BQ18" s="4"/>
-      <c r="BR18" s="4"/>
-      <c r="BS18" s="4"/>
-      <c r="BT18" s="4"/>
-      <c r="BU18" s="4"/>
-    </row>
-    <row r="19" spans="1:73" s="7" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="5" t="s">
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="3"/>
+      <c r="AD18" s="3"/>
+      <c r="AE18" s="3"/>
+      <c r="AF18" s="3"/>
+      <c r="AG18" s="3"/>
+      <c r="AH18" s="3"/>
+      <c r="AI18" s="3"/>
+      <c r="AJ18" s="3"/>
+      <c r="AK18" s="3"/>
+      <c r="AL18" s="3"/>
+      <c r="AM18" s="3"/>
+      <c r="AN18" s="3"/>
+      <c r="AO18" s="3"/>
+      <c r="AP18" s="3"/>
+      <c r="AQ18" s="3"/>
+      <c r="AR18" s="3"/>
+      <c r="AS18" s="3"/>
+      <c r="AT18" s="3"/>
+      <c r="AU18" s="3"/>
+      <c r="AV18" s="3"/>
+      <c r="AW18" s="3"/>
+      <c r="AX18" s="3"/>
+      <c r="AY18" s="3"/>
+      <c r="AZ18" s="3"/>
+      <c r="BA18" s="3"/>
+      <c r="BB18" s="3"/>
+      <c r="BC18" s="3"/>
+      <c r="BD18" s="3"/>
+      <c r="BE18" s="3"/>
+      <c r="BF18" s="3"/>
+      <c r="BG18" s="3"/>
+      <c r="BH18" s="3"/>
+      <c r="BI18" s="3"/>
+      <c r="BJ18" s="3"/>
+      <c r="BK18" s="3"/>
+      <c r="BL18" s="3"/>
+      <c r="BM18" s="3"/>
+      <c r="BN18" s="3"/>
+      <c r="BO18" s="3"/>
+      <c r="BP18" s="3"/>
+      <c r="BQ18" s="3"/>
+      <c r="BR18" s="3"/>
+      <c r="BS18" s="3"/>
+      <c r="BT18" s="3"/>
+      <c r="BU18" s="3"/>
+    </row>
+    <row r="19" spans="1:73" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>26</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="4">
         <v>24</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="4">
         <v>68</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="4">
         <v>64</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="4">
         <v>4</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19" s="4">
         <v>61</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="5">
         <v>38.46153846</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="5">
         <v>41.666666669999998</v>
       </c>
-      <c r="M19" s="5">
-        <v>3</v>
-      </c>
-      <c r="N19" s="5">
-        <v>0</v>
-      </c>
-      <c r="O19" s="5">
-        <v>0</v>
-      </c>
-      <c r="P19" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="5">
-        <v>0</v>
-      </c>
-      <c r="R19" s="5"/>
-      <c r="S19" s="6">
+      <c r="M19" s="4">
+        <v>3</v>
+      </c>
+      <c r="N19" s="4">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4">
+        <v>0</v>
+      </c>
+      <c r="P19" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4"/>
+      <c r="S19" s="5">
         <v>22.76923077</v>
       </c>
-      <c r="T19" s="5">
-        <v>3</v>
-      </c>
-      <c r="U19" s="5" t="s">
+      <c r="T19" s="4">
+        <v>3</v>
+      </c>
+      <c r="U19" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4"/>
-      <c r="AB19" s="4"/>
-      <c r="AC19" s="4"/>
-      <c r="AD19" s="4"/>
-      <c r="AE19" s="4"/>
-      <c r="AF19" s="4"/>
-      <c r="AG19" s="4"/>
-      <c r="AH19" s="4"/>
-      <c r="AI19" s="4"/>
-      <c r="AJ19" s="4"/>
-      <c r="AK19" s="4"/>
-      <c r="AL19" s="4"/>
-      <c r="AM19" s="4"/>
-      <c r="AN19" s="4"/>
-      <c r="AO19" s="4"/>
-      <c r="AP19" s="4"/>
-      <c r="AQ19" s="4"/>
-      <c r="AR19" s="4"/>
-      <c r="AS19" s="4"/>
-      <c r="AT19" s="4"/>
-      <c r="AU19" s="4"/>
-      <c r="AV19" s="4"/>
-      <c r="AW19" s="4"/>
-      <c r="AX19" s="4"/>
-      <c r="AY19" s="4"/>
-      <c r="AZ19" s="4"/>
-      <c r="BA19" s="4"/>
-      <c r="BB19" s="4"/>
-      <c r="BC19" s="4"/>
-      <c r="BD19" s="4"/>
-      <c r="BE19" s="4"/>
-      <c r="BF19" s="4"/>
-      <c r="BG19" s="4"/>
-      <c r="BH19" s="4"/>
-      <c r="BI19" s="4"/>
-      <c r="BJ19" s="4"/>
-      <c r="BK19" s="4"/>
-      <c r="BL19" s="4"/>
-      <c r="BM19" s="4"/>
-      <c r="BN19" s="4"/>
-      <c r="BO19" s="4"/>
-      <c r="BP19" s="4"/>
-      <c r="BQ19" s="4"/>
-      <c r="BR19" s="4"/>
-      <c r="BS19" s="4"/>
-      <c r="BT19" s="4"/>
-      <c r="BU19" s="4"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
+      <c r="AR19" s="3"/>
+      <c r="AS19" s="3"/>
+      <c r="AT19" s="3"/>
+      <c r="AU19" s="3"/>
+      <c r="AV19" s="3"/>
+      <c r="AW19" s="3"/>
+      <c r="AX19" s="3"/>
+      <c r="AY19" s="3"/>
+      <c r="AZ19" s="3"/>
+      <c r="BA19" s="3"/>
+      <c r="BB19" s="3"/>
+      <c r="BC19" s="3"/>
+      <c r="BD19" s="3"/>
+      <c r="BE19" s="3"/>
+      <c r="BF19" s="3"/>
+      <c r="BG19" s="3"/>
+      <c r="BH19" s="3"/>
+      <c r="BI19" s="3"/>
+      <c r="BJ19" s="3"/>
+      <c r="BK19" s="3"/>
+      <c r="BL19" s="3"/>
+      <c r="BM19" s="3"/>
+      <c r="BN19" s="3"/>
+      <c r="BO19" s="3"/>
+      <c r="BP19" s="3"/>
+      <c r="BQ19" s="3"/>
+      <c r="BR19" s="3"/>
+      <c r="BS19" s="3"/>
+      <c r="BT19" s="3"/>
+      <c r="BU19" s="3"/>
     </row>
     <row r="20" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A20" s="3" t="s">
@@ -2229,10 +2213,10 @@
       <c r="J20" s="3">
         <v>59</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20" s="7">
         <v>38.46153846</v>
       </c>
-      <c r="L20" s="8">
+      <c r="L20" s="7">
         <v>43.47826087</v>
       </c>
       <c r="M20" s="3">
@@ -2250,7 +2234,7 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="8">
+      <c r="S20" s="7">
         <v>24.76923077</v>
       </c>
       <c r="T20" s="3">
@@ -2288,10 +2272,10 @@
       <c r="J21" s="3">
         <v>55</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="7">
         <v>38.46153846</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="7">
         <v>40.909090910000003</v>
       </c>
       <c r="M21" s="3">
@@ -2309,127 +2293,127 @@
       <c r="Q21" s="3">
         <v>0</v>
       </c>
-      <c r="S21" s="8">
+      <c r="S21" s="7">
         <v>28.76923077</v>
       </c>
       <c r="T21" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:73" s="11" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="9" t="s">
+    <row r="22" spans="1:73" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="8">
         <v>26</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="8">
         <v>26</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="8">
         <v>68</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="8">
         <v>70</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="8">
         <v>2</v>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="8">
         <v>65</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="9">
         <v>38.46153846</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="9">
         <v>42.30769231</v>
       </c>
-      <c r="M22" s="9">
-        <v>3</v>
-      </c>
-      <c r="N22" s="9">
-        <v>0</v>
-      </c>
-      <c r="O22" s="9">
-        <v>0</v>
-      </c>
-      <c r="P22" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="9">
-        <v>0</v>
-      </c>
-      <c r="R22" s="9"/>
-      <c r="S22" s="10">
+      <c r="M22" s="8">
+        <v>3</v>
+      </c>
+      <c r="N22" s="8">
+        <v>0</v>
+      </c>
+      <c r="O22" s="8">
+        <v>0</v>
+      </c>
+      <c r="P22" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0</v>
+      </c>
+      <c r="R22" s="8"/>
+      <c r="S22" s="9">
         <v>20.76923077</v>
       </c>
-      <c r="T22" s="9">
+      <c r="T22" s="8">
         <v>1</v>
       </c>
-      <c r="U22" s="9" t="s">
+      <c r="U22" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
-      <c r="X22" s="4"/>
-      <c r="Y22" s="4"/>
-      <c r="Z22" s="4"/>
-      <c r="AA22" s="4"/>
-      <c r="AB22" s="4"/>
-      <c r="AC22" s="4"/>
-      <c r="AD22" s="4"/>
-      <c r="AE22" s="4"/>
-      <c r="AF22" s="4"/>
-      <c r="AG22" s="4"/>
-      <c r="AH22" s="4"/>
-      <c r="AI22" s="4"/>
-      <c r="AJ22" s="4"/>
-      <c r="AK22" s="4"/>
-      <c r="AL22" s="4"/>
-      <c r="AM22" s="4"/>
-      <c r="AN22" s="4"/>
-      <c r="AO22" s="4"/>
-      <c r="AP22" s="4"/>
-      <c r="AQ22" s="4"/>
-      <c r="AR22" s="4"/>
-      <c r="AS22" s="4"/>
-      <c r="AT22" s="4"/>
-      <c r="AU22" s="4"/>
-      <c r="AV22" s="4"/>
-      <c r="AW22" s="4"/>
-      <c r="AX22" s="4"/>
-      <c r="AY22" s="4"/>
-      <c r="AZ22" s="4"/>
-      <c r="BA22" s="4"/>
-      <c r="BB22" s="4"/>
-      <c r="BC22" s="4"/>
-      <c r="BD22" s="4"/>
-      <c r="BE22" s="4"/>
-      <c r="BF22" s="4"/>
-      <c r="BG22" s="4"/>
-      <c r="BH22" s="4"/>
-      <c r="BI22" s="4"/>
-      <c r="BJ22" s="4"/>
-      <c r="BK22" s="4"/>
-      <c r="BL22" s="4"/>
-      <c r="BM22" s="4"/>
-      <c r="BN22" s="4"/>
-      <c r="BO22" s="4"/>
-      <c r="BP22" s="4"/>
-      <c r="BQ22" s="4"/>
-      <c r="BR22" s="4"/>
-      <c r="BS22" s="4"/>
-      <c r="BT22" s="4"/>
-      <c r="BU22" s="4"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+      <c r="AH22" s="3"/>
+      <c r="AI22" s="3"/>
+      <c r="AJ22" s="3"/>
+      <c r="AK22" s="3"/>
+      <c r="AL22" s="3"/>
+      <c r="AM22" s="3"/>
+      <c r="AN22" s="3"/>
+      <c r="AO22" s="3"/>
+      <c r="AP22" s="3"/>
+      <c r="AQ22" s="3"/>
+      <c r="AR22" s="3"/>
+      <c r="AS22" s="3"/>
+      <c r="AT22" s="3"/>
+      <c r="AU22" s="3"/>
+      <c r="AV22" s="3"/>
+      <c r="AW22" s="3"/>
+      <c r="AX22" s="3"/>
+      <c r="AY22" s="3"/>
+      <c r="AZ22" s="3"/>
+      <c r="BA22" s="3"/>
+      <c r="BB22" s="3"/>
+      <c r="BC22" s="3"/>
+      <c r="BD22" s="3"/>
+      <c r="BE22" s="3"/>
+      <c r="BF22" s="3"/>
+      <c r="BG22" s="3"/>
+      <c r="BH22" s="3"/>
+      <c r="BI22" s="3"/>
+      <c r="BJ22" s="3"/>
+      <c r="BK22" s="3"/>
+      <c r="BL22" s="3"/>
+      <c r="BM22" s="3"/>
+      <c r="BN22" s="3"/>
+      <c r="BO22" s="3"/>
+      <c r="BP22" s="3"/>
+      <c r="BQ22" s="3"/>
+      <c r="BR22" s="3"/>
+      <c r="BS22" s="3"/>
+      <c r="BT22" s="3"/>
+      <c r="BU22" s="3"/>
     </row>
     <row r="23" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
@@ -2462,10 +2446,10 @@
       <c r="J23" s="3">
         <v>59</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="7">
         <v>37.5</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="7">
         <v>43.47826087</v>
       </c>
       <c r="M23" s="3">
@@ -2486,7 +2470,7 @@
       <c r="R23" s="3">
         <v>204</v>
       </c>
-      <c r="S23" s="8">
+      <c r="S23" s="7">
         <v>33.75</v>
       </c>
       <c r="T23" s="3">
@@ -2524,10 +2508,10 @@
       <c r="J24" s="3">
         <v>59</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="7">
         <v>37.5</v>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="7">
         <v>38.46153846</v>
       </c>
       <c r="M24" s="3">
@@ -2545,7 +2529,7 @@
       <c r="Q24" s="3">
         <v>3</v>
       </c>
-      <c r="S24" s="8">
+      <c r="S24" s="7">
         <v>39.75</v>
       </c>
       <c r="T24" s="3">
@@ -2583,10 +2567,10 @@
       <c r="J25" s="3">
         <v>59</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="7">
         <v>37.5</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="7">
         <v>45.833333330000002</v>
       </c>
       <c r="M25" s="3">
@@ -2604,7 +2588,7 @@
       <c r="Q25" s="3">
         <v>3</v>
       </c>
-      <c r="S25" s="8">
+      <c r="S25" s="7">
         <v>37.75</v>
       </c>
       <c r="T25" s="3">
@@ -2642,10 +2626,10 @@
       <c r="J26" s="3">
         <v>59</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="7">
         <v>37.5</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="7">
         <v>44</v>
       </c>
       <c r="M26" s="3">
@@ -2663,7 +2647,7 @@
       <c r="Q26" s="3">
         <v>3</v>
       </c>
-      <c r="S26" s="8">
+      <c r="S26" s="7">
         <v>36.75</v>
       </c>
       <c r="T26" s="3">
@@ -2701,10 +2685,10 @@
       <c r="J27" s="3">
         <v>55</v>
       </c>
-      <c r="K27" s="8">
+      <c r="K27" s="7">
         <v>37.5</v>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="7">
         <v>40.909090910000003</v>
       </c>
       <c r="M27" s="3">
@@ -2722,363 +2706,363 @@
       <c r="Q27" s="3">
         <v>3</v>
       </c>
-      <c r="S27" s="8">
+      <c r="S27" s="7">
         <v>34.75</v>
       </c>
       <c r="T27" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:73" s="11" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="9" t="s">
+    <row r="28" spans="1:73" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="8">
         <v>24</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="8">
         <v>23</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="8">
         <v>62</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="8">
         <v>64</v>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="8">
         <v>2</v>
       </c>
-      <c r="J28" s="9">
+      <c r="J28" s="8">
         <v>59</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="9">
         <v>37.5</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L28" s="9">
         <v>43.47826087</v>
       </c>
-      <c r="M28" s="9">
-        <v>3</v>
-      </c>
-      <c r="N28" s="9">
-        <v>3</v>
-      </c>
-      <c r="O28" s="9">
-        <v>3</v>
-      </c>
-      <c r="P28" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="9">
-        <v>0</v>
-      </c>
-      <c r="R28" s="9">
+      <c r="M28" s="8">
+        <v>3</v>
+      </c>
+      <c r="N28" s="8">
+        <v>3</v>
+      </c>
+      <c r="O28" s="8">
+        <v>3</v>
+      </c>
+      <c r="P28" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>0</v>
+      </c>
+      <c r="R28" s="8">
         <v>72</v>
       </c>
-      <c r="S28" s="10">
+      <c r="S28" s="9">
         <v>15.75</v>
       </c>
-      <c r="T28" s="9">
+      <c r="T28" s="8">
         <v>1</v>
       </c>
-      <c r="U28" s="9" t="s">
+      <c r="U28" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="V28" s="4"/>
-      <c r="W28" s="4"/>
-      <c r="X28" s="4"/>
-      <c r="Y28" s="4"/>
-      <c r="Z28" s="4"/>
-      <c r="AA28" s="4"/>
-      <c r="AB28" s="4"/>
-      <c r="AC28" s="4"/>
-      <c r="AD28" s="4"/>
-      <c r="AE28" s="4"/>
-      <c r="AF28" s="4"/>
-      <c r="AG28" s="4"/>
-      <c r="AH28" s="4"/>
-      <c r="AI28" s="4"/>
-      <c r="AJ28" s="4"/>
-      <c r="AK28" s="4"/>
-      <c r="AL28" s="4"/>
-      <c r="AM28" s="4"/>
-      <c r="AN28" s="4"/>
-      <c r="AO28" s="4"/>
-      <c r="AP28" s="4"/>
-      <c r="AQ28" s="4"/>
-      <c r="AR28" s="4"/>
-      <c r="AS28" s="4"/>
-      <c r="AT28" s="4"/>
-      <c r="AU28" s="4"/>
-      <c r="AV28" s="4"/>
-      <c r="AW28" s="4"/>
-      <c r="AX28" s="4"/>
-      <c r="AY28" s="4"/>
-      <c r="AZ28" s="4"/>
-      <c r="BA28" s="4"/>
-      <c r="BB28" s="4"/>
-      <c r="BC28" s="4"/>
-      <c r="BD28" s="4"/>
-      <c r="BE28" s="4"/>
-      <c r="BF28" s="4"/>
-      <c r="BG28" s="4"/>
-      <c r="BH28" s="4"/>
-      <c r="BI28" s="4"/>
-      <c r="BJ28" s="4"/>
-      <c r="BK28" s="4"/>
-      <c r="BL28" s="4"/>
-      <c r="BM28" s="4"/>
-      <c r="BN28" s="4"/>
-      <c r="BO28" s="4"/>
-      <c r="BP28" s="4"/>
-      <c r="BQ28" s="4"/>
-      <c r="BR28" s="4"/>
-      <c r="BS28" s="4"/>
-      <c r="BT28" s="4"/>
-      <c r="BU28" s="4"/>
-    </row>
-    <row r="29" spans="1:73" s="14" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="12" t="s">
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="3"/>
+      <c r="AD28" s="3"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="3"/>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="3"/>
+      <c r="AJ28" s="3"/>
+      <c r="AK28" s="3"/>
+      <c r="AL28" s="3"/>
+      <c r="AM28" s="3"/>
+      <c r="AN28" s="3"/>
+      <c r="AO28" s="3"/>
+      <c r="AP28" s="3"/>
+      <c r="AQ28" s="3"/>
+      <c r="AR28" s="3"/>
+      <c r="AS28" s="3"/>
+      <c r="AT28" s="3"/>
+      <c r="AU28" s="3"/>
+      <c r="AV28" s="3"/>
+      <c r="AW28" s="3"/>
+      <c r="AX28" s="3"/>
+      <c r="AY28" s="3"/>
+      <c r="AZ28" s="3"/>
+      <c r="BA28" s="3"/>
+      <c r="BB28" s="3"/>
+      <c r="BC28" s="3"/>
+      <c r="BD28" s="3"/>
+      <c r="BE28" s="3"/>
+      <c r="BF28" s="3"/>
+      <c r="BG28" s="3"/>
+      <c r="BH28" s="3"/>
+      <c r="BI28" s="3"/>
+      <c r="BJ28" s="3"/>
+      <c r="BK28" s="3"/>
+      <c r="BL28" s="3"/>
+      <c r="BM28" s="3"/>
+      <c r="BN28" s="3"/>
+      <c r="BO28" s="3"/>
+      <c r="BP28" s="3"/>
+      <c r="BQ28" s="3"/>
+      <c r="BR28" s="3"/>
+      <c r="BS28" s="3"/>
+      <c r="BT28" s="3"/>
+      <c r="BU28" s="3"/>
+    </row>
+    <row r="29" spans="1:73" s="13" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="11">
         <v>24</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="11">
         <v>26</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="11">
         <v>62</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="11">
         <v>64</v>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="11">
         <v>2</v>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="11">
         <v>59</v>
       </c>
-      <c r="K29" s="13">
+      <c r="K29" s="12">
         <v>37.5</v>
       </c>
-      <c r="L29" s="13">
+      <c r="L29" s="12">
         <v>30.76923077</v>
       </c>
-      <c r="M29" s="12">
-        <v>3</v>
-      </c>
-      <c r="N29" s="12">
-        <v>0</v>
-      </c>
-      <c r="O29" s="12">
-        <v>3</v>
-      </c>
-      <c r="P29" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="12">
-        <v>3</v>
-      </c>
-      <c r="R29" s="12">
+      <c r="M29" s="11">
+        <v>3</v>
+      </c>
+      <c r="N29" s="11">
+        <v>0</v>
+      </c>
+      <c r="O29" s="11">
+        <v>3</v>
+      </c>
+      <c r="P29" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="11">
+        <v>3</v>
+      </c>
+      <c r="R29" s="11">
         <v>178</v>
       </c>
-      <c r="S29" s="13">
+      <c r="S29" s="12">
         <v>25.115384615</v>
       </c>
-      <c r="T29" s="12">
+      <c r="T29" s="11">
         <v>2</v>
       </c>
-      <c r="U29" s="12" t="s">
+      <c r="U29" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="V29" s="4"/>
-      <c r="W29" s="4"/>
-      <c r="X29" s="4"/>
-      <c r="Y29" s="4"/>
-      <c r="Z29" s="4"/>
-      <c r="AA29" s="4"/>
-      <c r="AB29" s="4"/>
-      <c r="AC29" s="4"/>
-      <c r="AD29" s="4"/>
-      <c r="AE29" s="4"/>
-      <c r="AF29" s="4"/>
-      <c r="AG29" s="4"/>
-      <c r="AH29" s="4"/>
-      <c r="AI29" s="4"/>
-      <c r="AJ29" s="4"/>
-      <c r="AK29" s="4"/>
-      <c r="AL29" s="4"/>
-      <c r="AM29" s="4"/>
-      <c r="AN29" s="4"/>
-      <c r="AO29" s="4"/>
-      <c r="AP29" s="4"/>
-      <c r="AQ29" s="4"/>
-      <c r="AR29" s="4"/>
-      <c r="AS29" s="4"/>
-      <c r="AT29" s="4"/>
-      <c r="AU29" s="4"/>
-      <c r="AV29" s="4"/>
-      <c r="AW29" s="4"/>
-      <c r="AX29" s="4"/>
-      <c r="AY29" s="4"/>
-      <c r="AZ29" s="4"/>
-      <c r="BA29" s="4"/>
-      <c r="BB29" s="4"/>
-      <c r="BC29" s="4"/>
-      <c r="BD29" s="4"/>
-      <c r="BE29" s="4"/>
-      <c r="BF29" s="4"/>
-      <c r="BG29" s="4"/>
-      <c r="BH29" s="4"/>
-      <c r="BI29" s="4"/>
-      <c r="BJ29" s="4"/>
-      <c r="BK29" s="4"/>
-      <c r="BL29" s="4"/>
-      <c r="BM29" s="4"/>
-      <c r="BN29" s="4"/>
-      <c r="BO29" s="4"/>
-      <c r="BP29" s="4"/>
-      <c r="BQ29" s="4"/>
-      <c r="BR29" s="4"/>
-      <c r="BS29" s="4"/>
-      <c r="BT29" s="4"/>
-      <c r="BU29" s="4"/>
-    </row>
-    <row r="30" spans="1:73" s="7" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="5" t="s">
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
+      <c r="AB29" s="3"/>
+      <c r="AC29" s="3"/>
+      <c r="AD29" s="3"/>
+      <c r="AE29" s="3"/>
+      <c r="AF29" s="3"/>
+      <c r="AG29" s="3"/>
+      <c r="AH29" s="3"/>
+      <c r="AI29" s="3"/>
+      <c r="AJ29" s="3"/>
+      <c r="AK29" s="3"/>
+      <c r="AL29" s="3"/>
+      <c r="AM29" s="3"/>
+      <c r="AN29" s="3"/>
+      <c r="AO29" s="3"/>
+      <c r="AP29" s="3"/>
+      <c r="AQ29" s="3"/>
+      <c r="AR29" s="3"/>
+      <c r="AS29" s="3"/>
+      <c r="AT29" s="3"/>
+      <c r="AU29" s="3"/>
+      <c r="AV29" s="3"/>
+      <c r="AW29" s="3"/>
+      <c r="AX29" s="3"/>
+      <c r="AY29" s="3"/>
+      <c r="AZ29" s="3"/>
+      <c r="BA29" s="3"/>
+      <c r="BB29" s="3"/>
+      <c r="BC29" s="3"/>
+      <c r="BD29" s="3"/>
+      <c r="BE29" s="3"/>
+      <c r="BF29" s="3"/>
+      <c r="BG29" s="3"/>
+      <c r="BH29" s="3"/>
+      <c r="BI29" s="3"/>
+      <c r="BJ29" s="3"/>
+      <c r="BK29" s="3"/>
+      <c r="BL29" s="3"/>
+      <c r="BM29" s="3"/>
+      <c r="BN29" s="3"/>
+      <c r="BO29" s="3"/>
+      <c r="BP29" s="3"/>
+      <c r="BQ29" s="3"/>
+      <c r="BR29" s="3"/>
+      <c r="BS29" s="3"/>
+      <c r="BT29" s="3"/>
+      <c r="BU29" s="3"/>
+    </row>
+    <row r="30" spans="1:73" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="4">
         <v>24</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="4">
         <v>26</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="4">
         <v>62</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="4">
         <v>64</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="4">
         <v>2</v>
       </c>
-      <c r="J30" s="5">
+      <c r="J30" s="4">
         <v>59</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="5">
         <v>37.5</v>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="5">
         <v>30.76923077</v>
       </c>
-      <c r="M30" s="5">
-        <v>3</v>
-      </c>
-      <c r="N30" s="5">
-        <v>0</v>
-      </c>
-      <c r="O30" s="5">
-        <v>3</v>
-      </c>
-      <c r="P30" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5">
-        <v>3</v>
-      </c>
-      <c r="R30" s="5">
+      <c r="M30" s="4">
+        <v>3</v>
+      </c>
+      <c r="N30" s="4">
+        <v>0</v>
+      </c>
+      <c r="O30" s="4">
+        <v>3</v>
+      </c>
+      <c r="P30" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>3</v>
+      </c>
+      <c r="R30" s="4">
         <v>178</v>
       </c>
-      <c r="S30" s="6">
+      <c r="S30" s="5">
         <v>25.115384615</v>
       </c>
-      <c r="T30" s="5">
-        <v>3</v>
-      </c>
-      <c r="U30" s="5" t="s">
+      <c r="T30" s="4">
+        <v>3</v>
+      </c>
+      <c r="U30" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="V30" s="4"/>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4"/>
-      <c r="Y30" s="4"/>
-      <c r="Z30" s="4"/>
-      <c r="AA30" s="4"/>
-      <c r="AB30" s="4"/>
-      <c r="AC30" s="4"/>
-      <c r="AD30" s="4"/>
-      <c r="AE30" s="4"/>
-      <c r="AF30" s="4"/>
-      <c r="AG30" s="4"/>
-      <c r="AH30" s="4"/>
-      <c r="AI30" s="4"/>
-      <c r="AJ30" s="4"/>
-      <c r="AK30" s="4"/>
-      <c r="AL30" s="4"/>
-      <c r="AM30" s="4"/>
-      <c r="AN30" s="4"/>
-      <c r="AO30" s="4"/>
-      <c r="AP30" s="4"/>
-      <c r="AQ30" s="4"/>
-      <c r="AR30" s="4"/>
-      <c r="AS30" s="4"/>
-      <c r="AT30" s="4"/>
-      <c r="AU30" s="4"/>
-      <c r="AV30" s="4"/>
-      <c r="AW30" s="4"/>
-      <c r="AX30" s="4"/>
-      <c r="AY30" s="4"/>
-      <c r="AZ30" s="4"/>
-      <c r="BA30" s="4"/>
-      <c r="BB30" s="4"/>
-      <c r="BC30" s="4"/>
-      <c r="BD30" s="4"/>
-      <c r="BE30" s="4"/>
-      <c r="BF30" s="4"/>
-      <c r="BG30" s="4"/>
-      <c r="BH30" s="4"/>
-      <c r="BI30" s="4"/>
-      <c r="BJ30" s="4"/>
-      <c r="BK30" s="4"/>
-      <c r="BL30" s="4"/>
-      <c r="BM30" s="4"/>
-      <c r="BN30" s="4"/>
-      <c r="BO30" s="4"/>
-      <c r="BP30" s="4"/>
-      <c r="BQ30" s="4"/>
-      <c r="BR30" s="4"/>
-      <c r="BS30" s="4"/>
-      <c r="BT30" s="4"/>
-      <c r="BU30" s="4"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
+      <c r="AB30" s="3"/>
+      <c r="AC30" s="3"/>
+      <c r="AD30" s="3"/>
+      <c r="AE30" s="3"/>
+      <c r="AF30" s="3"/>
+      <c r="AG30" s="3"/>
+      <c r="AH30" s="3"/>
+      <c r="AI30" s="3"/>
+      <c r="AJ30" s="3"/>
+      <c r="AK30" s="3"/>
+      <c r="AL30" s="3"/>
+      <c r="AM30" s="3"/>
+      <c r="AN30" s="3"/>
+      <c r="AO30" s="3"/>
+      <c r="AP30" s="3"/>
+      <c r="AQ30" s="3"/>
+      <c r="AR30" s="3"/>
+      <c r="AS30" s="3"/>
+      <c r="AT30" s="3"/>
+      <c r="AU30" s="3"/>
+      <c r="AV30" s="3"/>
+      <c r="AW30" s="3"/>
+      <c r="AX30" s="3"/>
+      <c r="AY30" s="3"/>
+      <c r="AZ30" s="3"/>
+      <c r="BA30" s="3"/>
+      <c r="BB30" s="3"/>
+      <c r="BC30" s="3"/>
+      <c r="BD30" s="3"/>
+      <c r="BE30" s="3"/>
+      <c r="BF30" s="3"/>
+      <c r="BG30" s="3"/>
+      <c r="BH30" s="3"/>
+      <c r="BI30" s="3"/>
+      <c r="BJ30" s="3"/>
+      <c r="BK30" s="3"/>
+      <c r="BL30" s="3"/>
+      <c r="BM30" s="3"/>
+      <c r="BN30" s="3"/>
+      <c r="BO30" s="3"/>
+      <c r="BP30" s="3"/>
+      <c r="BQ30" s="3"/>
+      <c r="BR30" s="3"/>
+      <c r="BS30" s="3"/>
+      <c r="BT30" s="3"/>
+      <c r="BU30" s="3"/>
     </row>
     <row r="31" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A31" s="3" t="s">
@@ -3111,10 +3095,10 @@
       <c r="J31" s="3">
         <v>59</v>
       </c>
-      <c r="K31" s="8">
+      <c r="K31" s="7">
         <v>37.5</v>
       </c>
-      <c r="L31" s="8">
+      <c r="L31" s="7">
         <v>45.833333330000002</v>
       </c>
       <c r="M31" s="3">
@@ -3135,7 +3119,7 @@
       <c r="R31" s="3">
         <v>204</v>
       </c>
-      <c r="S31" s="8">
+      <c r="S31" s="7">
         <v>37.75</v>
       </c>
       <c r="T31" s="3">
@@ -3173,10 +3157,10 @@
       <c r="J32" s="3">
         <v>59</v>
       </c>
-      <c r="K32" s="8">
+      <c r="K32" s="7">
         <v>37.5</v>
       </c>
-      <c r="L32" s="8">
+      <c r="L32" s="7">
         <v>42.30769231</v>
       </c>
       <c r="M32" s="3">
@@ -3194,258 +3178,258 @@
       <c r="Q32" s="3">
         <v>3</v>
       </c>
-      <c r="S32" s="8">
+      <c r="S32" s="7">
         <v>44.25</v>
       </c>
       <c r="T32" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="27">
+    <row r="33" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="18">
         <v>45988.487511574072</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="10">
         <v>20</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="10">
         <v>20</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="10">
         <v>62</v>
       </c>
-      <c r="H33" s="11">
+      <c r="H33" s="10">
         <v>62</v>
       </c>
-      <c r="I33" s="11">
-        <v>0</v>
-      </c>
-      <c r="J33" s="11">
-        <v>55</v>
-      </c>
-      <c r="K33" s="11">
-        <v>55</v>
-      </c>
-      <c r="L33" s="11">
-        <v>3</v>
-      </c>
-      <c r="M33" s="11">
-        <v>0</v>
-      </c>
-      <c r="N33" s="11">
-        <v>0</v>
-      </c>
-      <c r="O33" s="11">
-        <v>0</v>
-      </c>
-      <c r="P33" s="11">
+      <c r="I33" s="10">
+        <v>0</v>
+      </c>
+      <c r="J33" s="10">
+        <v>55</v>
+      </c>
+      <c r="K33" s="10">
+        <v>55</v>
+      </c>
+      <c r="L33" s="10">
+        <v>3</v>
+      </c>
+      <c r="M33" s="10">
+        <v>0</v>
+      </c>
+      <c r="N33" s="10">
+        <v>0</v>
+      </c>
+      <c r="O33" s="10">
+        <v>0</v>
+      </c>
+      <c r="P33" s="10">
         <v>5</v>
       </c>
-      <c r="Q33" s="11">
+      <c r="Q33" s="10">
         <v>59</v>
       </c>
-      <c r="R33" s="11">
+      <c r="R33" s="10">
         <v>84</v>
       </c>
-      <c r="S33" s="28" t="s">
+      <c r="S33" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="T33" s="11" t="s">
+      <c r="T33" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="V33" s="11" t="s">
+      <c r="V33" s="10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="27">
+    <row r="34" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="18">
         <v>45988.535428240742</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="10">
         <v>20</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="10">
         <v>20</v>
       </c>
-      <c r="G34" s="11">
+      <c r="G34" s="10">
         <v>60</v>
       </c>
-      <c r="H34" s="11">
+      <c r="H34" s="10">
         <v>62</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="10">
         <v>2</v>
       </c>
-      <c r="J34" s="11">
+      <c r="J34" s="10">
         <v>50</v>
       </c>
-      <c r="K34" s="11">
-        <v>55</v>
-      </c>
-      <c r="L34" s="11">
-        <v>0</v>
-      </c>
-      <c r="M34" s="11">
-        <v>0</v>
-      </c>
-      <c r="N34" s="11">
-        <v>0</v>
-      </c>
-      <c r="O34" s="11">
-        <v>0</v>
-      </c>
-      <c r="P34" s="11">
+      <c r="K34" s="10">
+        <v>55</v>
+      </c>
+      <c r="L34" s="10">
+        <v>0</v>
+      </c>
+      <c r="M34" s="10">
+        <v>0</v>
+      </c>
+      <c r="N34" s="10">
+        <v>0</v>
+      </c>
+      <c r="O34" s="10">
+        <v>0</v>
+      </c>
+      <c r="P34" s="10">
         <v>5</v>
       </c>
-      <c r="Q34" s="11">
+      <c r="Q34" s="10">
         <v>57</v>
       </c>
-      <c r="R34" s="11">
+      <c r="R34" s="10">
         <v>117</v>
       </c>
-      <c r="S34" s="28" t="s">
+      <c r="S34" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="T34" s="11" t="s">
+      <c r="T34" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="U34" s="11" t="s">
+      <c r="U34" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="V34" s="11" t="s">
+      <c r="V34" s="10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="29"/>
-      <c r="S35" s="30"/>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A35" s="20"/>
+      <c r="S35" s="7"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
       <c r="G38" s="24"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C39" s="25" t="s">
+      <c r="C39" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="26"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="24"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C40" s="23" t="s">
+      <c r="C40" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
       <c r="G40" s="24"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
       <c r="G41" s="24"/>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B42" s="18"/>
-      <c r="C42" s="25" t="s">
+      <c r="B42" s="15"/>
+      <c r="C42" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="26"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="24"/>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="20" t="s">
+      <c r="C43" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B44" s="22" t="s">
+      <c r="B44" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="21" t="s">
+      <c r="C44" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="14" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="C37:G37"/>
     <mergeCell ref="C43:G43"/>
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C39:G39"/>
     <mergeCell ref="C40:G40"/>
     <mergeCell ref="C42:G42"/>
     <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
